--- a/reports/Debug-purgatory-20260105/For The Week Ending (Actual)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260105/For The Week Ending (Actual)_Revenue.xlsx
@@ -94,7 +94,7 @@
     <t>D4053</t>
   </si>
   <si>
-    <t>D4054</t>
+    <t xml:space="preserve">D4054                    </t>
   </si>
   <si>
     <t>D4055</t>
@@ -124,7 +124,7 @@
     <t>D5209</t>
   </si>
   <si>
-    <t>D6720</t>
+    <t xml:space="preserve">D6720                    </t>
   </si>
   <si>
     <t>revenue</t>
